--- a/medical_surveys_questionnaires/024_pituitary_adenoma_knowledge_quiz--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/024_pituitary_adenoma_knowledge_quiz--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,92 +515,92 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What is a pituitary adenoma?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is a pituitary adenoma?</t>
+          <t>What is the most common type of pituitary adenoma?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the most common type of pituitary adenoma?</t>
+          <t>What is the treatment for pituitary adenoma?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the treatment for pituitary adenoma?</t>
+          <t>What is the typical treatment for a large pituitary adenoma?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the typical treatment for a large pituitary adenoma?</t>
+          <t>What is the typical treatment for a small pituitary adenoma?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,202 +635,202 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the typical treatment for a small pituitary adenoma?</t>
+          <t>What are the typical side effects of treatment for pituitary adenoma?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the typical side effect of radiotherapy for pituitary adenoma?</t>
+          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the typical side effect of surgery for pituitary adenoma?</t>
+          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the typical side effect of chemotherapy for pituitary adenoma?</t>
+          <t>What are the possible causes of pituitary adenoma?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>introduction_2</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Introduction 2</t>
+          <t>What is the typical age range for pituitary adenoma diagnosis?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
+          <t>What is the typical treatment for pituitary adenoma in the presence of other health conditions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
+          <t>What is the expected prognosis for pituitary adenoma?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
+          <t>What is the typical follow-up care for pituitary adenoma?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
+          <t>What are the possible complications of pituitary adenoma treatment?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,248 +842,87 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
+          <t>What is the typical outcome for pituitary adenoma?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
+          <t>What are the typical tests and exams for pituitary adenoma diagnosis?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>question_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
+          <t>What is the typical treatment for pituitary adenoma in pregnancy?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>question_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
+          <t>What is the typical treatment for pituitary adenoma in children?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too small to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is the typical treatment for pituitary adenoma when it is too large to be removed surgically?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>adenoma</t>
+          <t>microadenoma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adenoma</t>
+          <t>Microadenoma</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroadenoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Macroadenoma</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>chemotherapy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Chemotherapy</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1267,87 +1106,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>surgery</t>
+          <t>radiotherapy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>surgery</t>
+          <t>chemotherapy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Chemotherapy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,92 +1203,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>radiotherapy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>chemotherapy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Chemotherapy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>genetic_mutation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Genetic mutation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>radiation_exposure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Radiation exposure</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,340 +1305,255 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>surgery</t>
+          <t>radiotherapy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>regular_check-ups</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Regular check-ups</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>infection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Infection</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>bleeding</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Bleeding</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Recovery</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>death</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Death</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>mri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>MRI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>radiotherapy</t>
+          <t>ct_scan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>CT scan</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>radiotherapy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chemotherapy</t>
+          <t>radiotherapy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chemotherapy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>radiotherapy</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
           <t>Radiotherapy</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>radiotherapy</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Radiotherapy</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
